--- a/6.1 Myrmidon disturbance/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/6.1 Myrmidon disturbance/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>72.56144146501978</v>
+        <v>71.43801306649405</v>
       </c>
       <c r="C3" t="n">
-        <v>55.90033035390867</v>
+        <v>54.77690195538294</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.30082833354698</v>
+        <v>0.2949583397874163</v>
       </c>
       <c r="F3" t="n">
-        <v>10.50402112139164</v>
+        <v>10.50408438181848</v>
       </c>
       <c r="G3" t="n">
-        <v>44.11688870984488</v>
+        <v>43.99916683210269</v>
       </c>
       <c r="H3" t="n">
-        <v>9.403599861055371</v>
+        <v>9.403656494199401</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8336524699517173</v>
+        <v>0.8336574906205143</v>
       </c>
       <c r="J3" t="n">
-        <v>6.402450969229189</v>
+        <v>6.40248952796555</v>
       </c>
       <c r="K3" t="n">
-        <v>27.43855853498022</v>
+        <v>28.56198693350595</v>
       </c>
       <c r="L3" t="n">
         <v>16.63333333333333</v>
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.99450184907704</v>
+        <v>87.1997388347374</v>
       </c>
       <c r="C4" t="n">
-        <v>64.47721407473554</v>
+        <v>63.42636156009989</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>7.440093797001771</v>
+        <v>6.494547095598265</v>
       </c>
       <c r="F4" t="n">
-        <v>10.53379886860419</v>
+        <v>10.53513502862187</v>
       </c>
       <c r="G4" t="n">
-        <v>46.68610723557629</v>
+        <v>46.58417122281128</v>
       </c>
       <c r="H4" t="n">
-        <v>9.430258034750418</v>
+        <v>9.431454216099576</v>
       </c>
       <c r="I4" t="n">
-        <v>7.483642697995148</v>
+        <v>7.73301563511309</v>
       </c>
       <c r="J4" t="n">
-        <v>6.420601215149222</v>
+        <v>6.421415636493328</v>
       </c>
       <c r="K4" t="n">
-        <v>12.00549815092297</v>
+        <v>12.8002611652626</v>
       </c>
       <c r="L4" t="n">
-        <v>23.26853819550094</v>
+        <v>23.51636981488033</v>
       </c>
       <c r="M4" t="n">
-        <v>99.75125042115945</v>
+        <v>99.74299254024281</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>87.47895667714592</v>
+        <v>86.3127673954579</v>
       </c>
       <c r="C5" t="n">
-        <v>65.18384954841711</v>
+        <v>63.80091185707316</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>8.649097793828082</v>
+        <v>7.478662069593231</v>
       </c>
       <c r="F5" t="n">
-        <v>10.55889028779379</v>
+        <v>10.56141915975844</v>
       </c>
       <c r="G5" t="n">
-        <v>46.1311288412546</v>
+        <v>45.92000766051021</v>
       </c>
       <c r="H5" t="n">
-        <v>9.452720829072534</v>
+        <v>9.454984771593274</v>
       </c>
       <c r="I5" t="n">
-        <v>6.251223892636884</v>
+        <v>6.460257293769014</v>
       </c>
       <c r="J5" t="n">
-        <v>6.435895032560024</v>
+        <v>6.437436440233719</v>
       </c>
       <c r="K5" t="n">
-        <v>12.5210433228541</v>
+        <v>13.68723260454211</v>
       </c>
       <c r="L5" t="n">
-        <v>22.0872281648956</v>
+        <v>22.29704954852048</v>
       </c>
       <c r="M5" t="n">
-        <v>99.7921210361668</v>
+        <v>99.78519401013574</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>86.30309781681541</v>
+        <v>84.73852438587031</v>
       </c>
       <c r="C6" t="n">
-        <v>65.03148360319</v>
+        <v>63.28310383774219</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>9.371459091819304</v>
+        <v>8.172749545583091</v>
       </c>
       <c r="F6" t="n">
-        <v>10.58017800747715</v>
+        <v>10.5838326443677</v>
       </c>
       <c r="G6" t="n">
-        <v>45.2109561144497</v>
+        <v>44.66082129563585</v>
       </c>
       <c r="H6" t="n">
-        <v>9.471778406693831</v>
+        <v>9.475050176862513</v>
       </c>
       <c r="I6" t="n">
-        <v>5.21985579181792</v>
+        <v>5.394972730663692</v>
       </c>
       <c r="J6" t="n">
-        <v>6.448870404557502</v>
+        <v>6.451097992757456</v>
       </c>
       <c r="K6" t="n">
-        <v>13.69690218318459</v>
+        <v>15.26147561412971</v>
       </c>
       <c r="L6" t="n">
-        <v>21.09796910549663</v>
+        <v>21.2759689566345</v>
       </c>
       <c r="M6" t="n">
-        <v>99.82635489187122</v>
+        <v>99.8205484085064</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84.89930659198995</v>
+        <v>82.96373006627717</v>
       </c>
       <c r="C7" t="n">
-        <v>64.48378196000651</v>
+        <v>62.39191093414125</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10.02614316538594</v>
+        <v>8.663159492491298</v>
       </c>
       <c r="F7" t="n">
-        <v>10.59827836624792</v>
+        <v>10.60298519584663</v>
       </c>
       <c r="G7" t="n">
-        <v>43.9696780040833</v>
+        <v>43.23867093035262</v>
       </c>
       <c r="H7" t="n">
-        <v>9.487982537402898</v>
+        <v>9.49219627056746</v>
       </c>
       <c r="I7" t="n">
-        <v>4.357321514680671</v>
+        <v>4.503946248122168</v>
       </c>
       <c r="J7" t="n">
-        <v>6.459903004189208</v>
+        <v>6.462771928896994</v>
       </c>
       <c r="K7" t="n">
-        <v>15.10069340801006</v>
+        <v>17.03626993372283</v>
       </c>
       <c r="L7" t="n">
-        <v>20.27052863776627</v>
+        <v>20.42195877850638</v>
       </c>
       <c r="M7" t="n">
-        <v>99.85500400578285</v>
+        <v>99.85013964637047</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82.79876902146052</v>
+        <v>80.47411324549047</v>
       </c>
       <c r="C8" t="n">
-        <v>63.09874550889337</v>
+        <v>60.64074688792083</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10.32346428670144</v>
+        <v>8.886971036233932</v>
       </c>
       <c r="F8" t="n">
-        <v>10.61379379822568</v>
+        <v>10.61949486451282</v>
       </c>
       <c r="G8" t="n">
-        <v>42.25386132281975</v>
+        <v>41.22870332393088</v>
       </c>
       <c r="H8" t="n">
-        <v>9.501872543173461</v>
+        <v>9.506976354897189</v>
       </c>
       <c r="I8" t="n">
-        <v>3.63641704114549</v>
+        <v>3.759132700879278</v>
       </c>
       <c r="J8" t="n">
-        <v>6.469360029394697</v>
+        <v>6.472834965036384</v>
       </c>
       <c r="K8" t="n">
-        <v>17.20123097853949</v>
+        <v>19.52588675450952</v>
       </c>
       <c r="L8" t="n">
-        <v>19.578986803826</v>
+        <v>19.70825673956626</v>
       </c>
       <c r="M8" t="n">
-        <v>99.87896329125886</v>
+        <v>99.87489038199661</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80.00320316370956</v>
+        <v>77.23812049695334</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90061147237722</v>
+        <v>58.0212782401515</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>10.29261322380085</v>
+        <v>8.847197657070319</v>
       </c>
       <c r="F9" t="n">
-        <v>10.62721165457821</v>
+        <v>10.63387108914953</v>
       </c>
       <c r="G9" t="n">
-        <v>40.05777656309429</v>
+        <v>38.61875625536729</v>
       </c>
       <c r="H9" t="n">
-        <v>9.513884719336684</v>
+        <v>9.51984649885768</v>
       </c>
       <c r="I9" t="n">
-        <v>3.034178470585176</v>
+        <v>3.136851380264987</v>
       </c>
       <c r="J9" t="n">
-        <v>6.477538532314339</v>
+        <v>6.481597616243526</v>
       </c>
       <c r="K9" t="n">
-        <v>19.99679683629045</v>
+        <v>22.76187950304665</v>
       </c>
       <c r="L9" t="n">
-        <v>19.00158010685606</v>
+        <v>19.11242190399964</v>
       </c>
       <c r="M9" t="n">
-        <v>99.89898841552375</v>
+        <v>99.89557964719779</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>76.61476968484098</v>
+        <v>73.52190287374702</v>
       </c>
       <c r="C10" t="n">
-        <v>58.01058163907494</v>
+        <v>54.81928118119541</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09844162680771</v>
+        <v>8.600397001066446</v>
       </c>
       <c r="F10" t="n">
-        <v>10.63891536250558</v>
+        <v>10.6464888155347</v>
       </c>
       <c r="G10" t="n">
-        <v>37.33711148351149</v>
+        <v>35.63744173244815</v>
       </c>
       <c r="H10" t="n">
-        <v>9.5243623245288</v>
+        <v>9.531142368192969</v>
       </c>
       <c r="I10" t="n">
-        <v>2.531266666531628</v>
+        <v>2.617144535607423</v>
       </c>
       <c r="J10" t="n">
-        <v>6.484672220955781</v>
+        <v>6.48928842089734</v>
       </c>
       <c r="K10" t="n">
-        <v>23.38523031515902</v>
+        <v>26.47809712625298</v>
       </c>
       <c r="L10" t="n">
-        <v>18.51990531047201</v>
+        <v>18.61548693198869</v>
       </c>
       <c r="M10" t="n">
-        <v>99.91571726470596</v>
+        <v>99.91286523943708</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>72.64558335152519</v>
+        <v>69.37122182895179</v>
       </c>
       <c r="C11" t="n">
-        <v>54.45684695430506</v>
+        <v>51.09713880086619</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>9.767488819439102</v>
+        <v>8.165501393356834</v>
       </c>
       <c r="F11" t="n">
-        <v>10.64922264290295</v>
+        <v>10.65765764419724</v>
       </c>
       <c r="G11" t="n">
-        <v>34.09289481676156</v>
+        <v>32.32758383863698</v>
       </c>
       <c r="H11" t="n">
-        <v>9.533589794598827</v>
+        <v>9.541141129090867</v>
       </c>
       <c r="I11" t="n">
-        <v>2.111432524053345</v>
+        <v>2.183241735778208</v>
       </c>
       <c r="J11" t="n">
-        <v>6.490954753769416</v>
+        <v>6.496096087891654</v>
       </c>
       <c r="K11" t="n">
-        <v>27.35441664847479</v>
+        <v>30.62877817104823</v>
       </c>
       <c r="L11" t="n">
-        <v>18.11842343426094</v>
+        <v>18.20138456876316</v>
       </c>
       <c r="M11" t="n">
-        <v>99.92968703704079</v>
+        <v>99.92730154067758</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68.26390590279308</v>
+        <v>64.91671838312092</v>
       </c>
       <c r="C12" t="n">
-        <v>50.42118334760113</v>
+        <v>46.99946744921829</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>9.315524864417064</v>
+        <v>7.666250311130995</v>
       </c>
       <c r="F12" t="n">
-        <v>10.65838009754496</v>
+        <v>10.66762340460988</v>
       </c>
       <c r="G12" t="n">
-        <v>30.4906364517614</v>
+        <v>28.70954198625089</v>
       </c>
       <c r="H12" t="n">
-        <v>9.541787896849767</v>
+        <v>9.550062857460272</v>
       </c>
       <c r="I12" t="n">
-        <v>1.761040151811544</v>
+        <v>1.821069367525719</v>
       </c>
       <c r="J12" t="n">
-        <v>6.496536440408355</v>
+        <v>6.502170456143164</v>
       </c>
       <c r="K12" t="n">
-        <v>31.7360940972069</v>
+        <v>35.08328161687907</v>
       </c>
       <c r="L12" t="n">
-        <v>17.78407165174603</v>
+        <v>17.85660533013103</v>
       </c>
       <c r="M12" t="n">
-        <v>99.94134909655406</v>
+        <v>99.9393543962284</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>63.43951914430794</v>
+        <v>60.00755852060527</v>
       </c>
       <c r="C13" t="n">
-        <v>45.88474356521208</v>
+        <v>42.38718214052134</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.498316831040029</v>
+        <v>6.890372598458468</v>
       </c>
       <c r="F13" t="n">
-        <v>10.66660504419043</v>
+        <v>10.67662360052355</v>
       </c>
       <c r="G13" t="n">
-        <v>26.75523040727365</v>
+        <v>24.85594769737037</v>
       </c>
       <c r="H13" t="n">
-        <v>9.549151182418091</v>
+        <v>9.558120175706799</v>
       </c>
       <c r="I13" t="n">
-        <v>1.468665938164911</v>
+        <v>1.518838158703153</v>
       </c>
       <c r="J13" t="n">
-        <v>6.501549741220831</v>
+        <v>6.507656289842926</v>
       </c>
       <c r="K13" t="n">
-        <v>36.56048085569207</v>
+        <v>39.99244147939473</v>
       </c>
       <c r="L13" t="n">
-        <v>17.50585779710108</v>
+        <v>17.56979111987487</v>
       </c>
       <c r="M13" t="n">
-        <v>99.95108221800521</v>
+        <v>99.94941473979094</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>59.00511202638074</v>
+        <v>55.62326621520054</v>
       </c>
       <c r="C14" t="n">
-        <v>41.68972654487759</v>
+        <v>38.249601335212</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>7.865525247903672</v>
+        <v>6.24548798018515</v>
       </c>
       <c r="F14" t="n">
-        <v>10.67398506307931</v>
+        <v>10.68472790928988</v>
       </c>
       <c r="G14" t="n">
-        <v>23.17906055391009</v>
+        <v>21.34841958527471</v>
       </c>
       <c r="H14" t="n">
-        <v>9.555758056470992</v>
+        <v>9.565375461649989</v>
       </c>
       <c r="I14" t="n">
-        <v>1.224735066568333</v>
+        <v>1.266659219805083</v>
       </c>
       <c r="J14" t="n">
-        <v>6.506048038448339</v>
+        <v>6.512596058995737</v>
       </c>
       <c r="K14" t="n">
-        <v>40.99488797361927</v>
+        <v>44.37673378479945</v>
       </c>
       <c r="L14" t="n">
-        <v>17.27458920544301</v>
+        <v>17.33147493113569</v>
       </c>
       <c r="M14" t="n">
-        <v>99.95920372393988</v>
+        <v>99.95781005114713</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>54.92055070286188</v>
+        <v>51.54545551321662</v>
       </c>
       <c r="C15" t="n">
-        <v>37.80411163395314</v>
+        <v>34.37674966440542</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>7.126811491763264</v>
+        <v>5.512537148728092</v>
       </c>
       <c r="F15" t="n">
-        <v>10.68060113877577</v>
+        <v>10.69202629689344</v>
       </c>
       <c r="G15" t="n">
-        <v>20.02013119511474</v>
+        <v>18.19566785029865</v>
       </c>
       <c r="H15" t="n">
-        <v>9.561681019475442</v>
+        <v>9.571909256266512</v>
       </c>
       <c r="I15" t="n">
-        <v>1.021245163621726</v>
+        <v>1.056270361018687</v>
       </c>
       <c r="J15" t="n">
-        <v>6.510080694110942</v>
+        <v>6.517044600011241</v>
       </c>
       <c r="K15" t="n">
-        <v>45.07944929713813</v>
+        <v>48.45454448678337</v>
       </c>
       <c r="L15" t="n">
-        <v>17.08241865039294</v>
+        <v>17.1335208704833</v>
       </c>
       <c r="M15" t="n">
-        <v>99.96597958148421</v>
+        <v>99.96481502167208</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>51.74714942365448</v>
+        <v>48.36301271914812</v>
       </c>
       <c r="C16" t="n">
-        <v>34.79598215250495</v>
+        <v>31.36449271865983</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>6.702566194278758</v>
+        <v>5.114734803004502</v>
       </c>
       <c r="F16" t="n">
-        <v>10.68645948351624</v>
+        <v>10.69851686664783</v>
       </c>
       <c r="G16" t="n">
-        <v>17.42604218499761</v>
+        <v>15.57028079153606</v>
       </c>
       <c r="H16" t="n">
-        <v>9.566925632862151</v>
+        <v>9.577719861570442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8515044332850648</v>
+        <v>0.880759639575364</v>
       </c>
       <c r="J16" t="n">
-        <v>6.51365149471466</v>
+        <v>6.521000756813917</v>
       </c>
       <c r="K16" t="n">
-        <v>48.25285057634552</v>
+        <v>51.63698728085188</v>
       </c>
       <c r="L16" t="n">
-        <v>16.92279934993782</v>
+        <v>16.96917915712666</v>
       </c>
       <c r="M16" t="n">
-        <v>99.97163207878829</v>
+        <v>99.97065915663836</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>68.66496947493201</v>
+        <v>65.41024021590481</v>
       </c>
       <c r="C17" t="n">
-        <v>38.32205982517999</v>
+        <v>35.23522783235008</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9.614786260955892</v>
+        <v>8.159593578960793</v>
       </c>
       <c r="F17" t="n">
-        <v>10.75520677468282</v>
+        <v>10.76870521706873</v>
       </c>
       <c r="G17" t="n">
-        <v>18.19859725259767</v>
+        <v>16.5380921544502</v>
       </c>
       <c r="H17" t="n">
-        <v>10.28892204960547</v>
+        <v>10.50621661931887</v>
       </c>
       <c r="I17" t="n">
-        <v>13.25190253156919</v>
+        <v>12.87385041855956</v>
       </c>
       <c r="J17" t="n">
-        <v>6.555554605520953</v>
+        <v>6.563782227546652</v>
       </c>
       <c r="K17" t="n">
-        <v>31.33503052506799</v>
+        <v>34.58975978409519</v>
       </c>
       <c r="L17" t="n">
-        <v>29.90400310445442</v>
+        <v>29.74868101234107</v>
       </c>
       <c r="M17" t="n">
-        <v>99.56109345470242</v>
+        <v>99.57366862878632</v>
       </c>
     </row>
   </sheetData>
